--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487936_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487936_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2618</v>
+        <v>5.73</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5486</v>
+        <v>4.87</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7131999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="G2" t="n">
         <v>3.335</v>
@@ -610,13 +610,13 @@
         <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4489</v>
+        <v>0.0194</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.2657</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1383</v>
+        <v>0.2851</v>
       </c>
       <c r="V2" t="n">
         <v>1.7513</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7352</v>
+        <v>3.2144</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5445</v>
+        <v>1.2587</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1906</v>
+        <v>1.9557</v>
       </c>
       <c r="G3" t="n">
         <v>0.4718</v>
@@ -688,13 +688,13 @@
         <v>1.8731</v>
       </c>
       <c r="S3" t="n">
-        <v>3.0552</v>
+        <v>1.5345</v>
       </c>
       <c r="T3" t="n">
-        <v>2.087</v>
+        <v>0.8011</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>0.5838</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6513</v>
+        <v>2.368</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0011</v>
+        <v>1.8939</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6503</v>
+        <v>0.4741</v>
       </c>
       <c r="G4" t="n">
         <v>2.9707</v>
@@ -766,13 +766,13 @@
         <v>1.4568</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7431</v>
+        <v>0.4598</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2172</v>
+        <v>0.11</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5259</v>
+        <v>0.3498</v>
       </c>
       <c r="V4" t="n">
         <v>-0.23</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W. CABRAL BUERIBERI</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4985</v>
+        <v>1.4923</v>
       </c>
       <c r="E5" t="n">
-        <v>1.288</v>
+        <v>0.9432</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2105</v>
+        <v>0.5491</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.6148</v>
+        <v>0.8027</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0154</v>
+        <v>1.695</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5994</v>
+        <v>-0.8923</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0674</v>
+        <v>1.9254</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9565</v>
+        <v>1.1808</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.8891</v>
+        <v>0.7446</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.6823</v>
+        <v>-1.1227</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.972</v>
+        <v>0.5142</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7103</v>
+        <v>-1.6369</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2081</v>
+        <v>0.4162</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.2487</v>
+        <v>-2.0812</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4568</v>
+        <v>2.4974</v>
       </c>
       <c r="S5" t="n">
-        <v>2.3839</v>
+        <v>0.2734</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0093</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3745</v>
+        <v>0.3419</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5213</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4599</v>
+        <v>1.1675</v>
       </c>
       <c r="X5" t="n">
-        <v>1.0614</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>N. DEDOVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.881</v>
+        <v>0.8938</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4494</v>
+        <v>0.1283</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4316</v>
+        <v>0.7655</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8027</v>
+        <v>-1.4872</v>
       </c>
       <c r="H6" t="n">
-        <v>1.695</v>
+        <v>0.642</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8923</v>
+        <v>-2.1292</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9254</v>
+        <v>-1.1074</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1808</v>
+        <v>0.4177</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7446</v>
+        <v>-1.5251</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1227</v>
+        <v>-0.3798</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5142</v>
+        <v>0.2243</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.6369</v>
+        <v>-0.6041</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4162</v>
+        <v>2.0812</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4974</v>
+        <v>2.0812</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3379</v>
+        <v>0.2998</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5624</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2245</v>
+        <v>0.2317</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4981</v>
+        <v>0.7609</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.25</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7482</v>
+        <v>0.6894</v>
       </c>
       <c r="G7" t="n">
         <v>0.0682</v>
@@ -1000,13 +1000,13 @@
         <v>0.4162</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0137</v>
+        <v>0.2765</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1305</v>
+        <v>0.191</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1442</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. DEDOVIC</t>
+          <t>W. CABRAL BUERIBERI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3095</v>
+        <v>0.1311</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5145999999999999</v>
+        <v>0.0674</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8242</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4872</v>
+        <v>-2.6148</v>
       </c>
       <c r="H8" t="n">
-        <v>0.642</v>
+        <v>-1.0154</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.1292</v>
+        <v>-1.5994</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1074</v>
+        <v>0.0674</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4177</v>
+        <v>0.9565</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.5251</v>
+        <v>-0.8891</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3798</v>
+        <v>-2.6823</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2243</v>
+        <v>-1.972</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6041</v>
+        <v>-0.7103</v>
       </c>
       <c r="P8" t="n">
-        <v>2.0812</v>
+        <v>0.2081</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.2487</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0812</v>
+        <v>1.4568</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2844</v>
+        <v>1.0164</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5748</v>
+        <v>0.7887</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2904</v>
+        <v>0.2277</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.5213</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1675</v>
+        <v>0.4599</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1675</v>
+        <v>1.0614</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. DIBBA</t>
+          <t>S. CECILIA PEREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1128</v>
+        <v>-0.0457</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.345</v>
+        <v>0.3084</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2322</v>
+        <v>-0.3541</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7336</v>
+        <v>0.3179</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.2028</v>
       </c>
       <c r="I9" t="n">
         <v>0.1151</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3256</v>
+        <v>2.2858</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2472</v>
+        <v>1.7461</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0784</v>
+        <v>0.5396</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5921</v>
+        <v>-1.9679</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6288</v>
+        <v>-1.5434</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0367</v>
+        <v>-0.4245</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4162</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0406</v>
+        <v>-2.2893</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6244</v>
+        <v>1.4568</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.07630000000000001</v>
+        <v>0.6989</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0776</v>
+        <v>0.312</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1539</v>
+        <v>0.3869</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3538</v>
+        <v>-0.23</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.7076</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3538</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. CECILIA PEREZ</t>
+          <t>L. DIBBA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3942</v>
+        <v>-0.0644</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1361</v>
+        <v>-0.2378</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5303</v>
+        <v>0.1734</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3179</v>
+        <v>0.7336</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2028</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="I10" t="n">
         <v>0.1151</v>
       </c>
       <c r="J10" t="n">
-        <v>2.2858</v>
+        <v>1.3256</v>
       </c>
       <c r="K10" t="n">
-        <v>1.7461</v>
+        <v>1.2472</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5396</v>
+        <v>0.0784</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9679</v>
+        <v>-0.5921</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5434</v>
+        <v>-0.6288</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4245</v>
+        <v>0.0367</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.8325</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2893</v>
+        <v>-1.0406</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4568</v>
+        <v>0.6244</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3503</v>
+        <v>-0.0279</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1396</v>
+        <v>0.1848</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2108</v>
+        <v>-0.2127</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.23</v>
+        <v>-0.3538</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.7076</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.23</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8638</v>
+        <v>-1.2143</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2395</v>
+        <v>-0.5314</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6242</v>
+        <v>-0.6829</v>
       </c>
       <c r="G11" t="n">
         <v>-0.6976</v>
@@ -1312,13 +1312,13 @@
         <v>1.2487</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2068</v>
+        <v>0.4427</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3138</v>
+        <v>0.3944</v>
       </c>
       <c r="U11" t="n">
-        <v>0.107</v>
+        <v>0.0483</v>
       </c>
       <c r="V11" t="n">
         <v>-1.1675</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3622</v>
+        <v>-1.8375</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8937</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4685</v>
+        <v>-1.1162</v>
       </c>
       <c r="G12" t="n">
         <v>-4.1651</v>
@@ -1390,13 +1390,13 @@
         <v>1.8731</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0111</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0743</v>
+        <v>0.2467</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0633</v>
+        <v>0.2891</v>
       </c>
       <c r="V12" t="n">
         <v>1.1675</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.1024</v>
+        <v>11.4286</v>
       </c>
       <c r="E13" t="n">
-        <v>7.724900000000003</v>
+        <v>8.050800000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>3.3778</v>
+        <v>3.3777</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2647999999999997</v>
+        <v>-0.2648000000000006</v>
       </c>
       <c r="H13" t="n">
         <v>10.2669</v>
@@ -1459,7 +1459,7 @@
         <v>-5.8578</v>
       </c>
       <c r="P13" t="n">
-        <v>3.121799999999999</v>
+        <v>3.1218</v>
       </c>
       <c r="Q13" t="n">
         <v>-13.5277</v>
@@ -1468,13 +1468,13 @@
         <v>16.6494</v>
       </c>
       <c r="S13" t="n">
-        <v>5.202999999999999</v>
+        <v>5.5293</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4363</v>
+        <v>2.7626</v>
       </c>
       <c r="U13" t="n">
-        <v>2.7666</v>
+        <v>2.7667</v>
       </c>
       <c r="V13" t="n">
         <v>3.0426</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7386</v>
+        <v>3.102</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3985</v>
+        <v>3.6484</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6599</v>
+        <v>-0.5464</v>
       </c>
       <c r="G14" t="n">
         <v>1.9722</v>
@@ -1546,13 +1546,13 @@
         <v>1.8731</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1233</v>
+        <v>-0.5133</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3849</v>
+        <v>-0.3652</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2616</v>
+        <v>-0.148</v>
       </c>
       <c r="V14" t="n">
         <v>-0.23</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1051</v>
+        <v>2.5122</v>
       </c>
       <c r="E15" t="n">
         <v>1.1675</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9376</v>
+        <v>1.3447</v>
       </c>
       <c r="G15" t="n">
         <v>2.3547</v>
@@ -1624,13 +1624,13 @@
         <v>1.2487</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0602</v>
+        <v>-0.6531</v>
       </c>
       <c r="T15" t="n">
         <v>-0.3791</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6811</v>
+        <v>-0.274</v>
       </c>
       <c r="V15" t="n">
         <v>-0.23</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4644</v>
+        <v>1.6302</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7232</v>
+        <v>0.8304</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7411</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>1.3476</v>
@@ -1702,13 +1702,13 @@
         <v>0.4162</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2995</v>
+        <v>-0.1336</v>
       </c>
       <c r="T16" t="n">
-        <v>0.09</v>
+        <v>0.1972</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3895</v>
+        <v>-0.3308</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3211</v>
+        <v>0.7726</v>
       </c>
       <c r="E17" t="n">
-        <v>2.528</v>
+        <v>1.7779</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2069</v>
+        <v>-1.0053</v>
       </c>
       <c r="G17" t="n">
         <v>1.6014</v>
@@ -1780,13 +1780,13 @@
         <v>1.0406</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6354</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.2343</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.349</v>
+        <v>-0.1474</v>
       </c>
       <c r="V17" t="n">
         <v>-0.7076</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ GONZÁLEZ</t>
+          <t>A. BURGOS CABALLERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.545</v>
+        <v>0.4217</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0816</v>
+        <v>1.058</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5366</v>
+        <v>-0.6363</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0059</v>
+        <v>-1.0177</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.262</v>
+        <v>-4.5904</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2679</v>
+        <v>3.5727</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3821</v>
+        <v>1.1626</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7631</v>
+        <v>-1.7977</v>
       </c>
       <c r="L18" t="n">
-        <v>1.6189</v>
+        <v>2.9603</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.3762</v>
+        <v>-2.1803</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.0251</v>
+        <v>-2.7927</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.351</v>
+        <v>0.6123</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2893</v>
+        <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4568</v>
+        <v>2.0812</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.426</v>
+        <v>-0.9987</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1744</v>
+        <v>-0.6915</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7484</v>
+        <v>-0.3072</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7076</v>
+        <v>1.3975</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.6275</v>
       </c>
       <c r="X18" t="n">
-        <v>0.7076</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BURGOS CABALLERO</t>
+          <t>J. JIMÉNEZ GONZÁLEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6093</v>
+        <v>-0.3845</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5222</v>
+        <v>-0.653</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1315</v>
+        <v>0.2685</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0177</v>
+        <v>0.0059</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.5904</v>
+        <v>-1.262</v>
       </c>
       <c r="I19" t="n">
-        <v>3.5727</v>
+        <v>1.2679</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1626</v>
+        <v>2.3821</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.7977</v>
+        <v>0.7631</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9603</v>
+        <v>1.6189</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.1803</v>
+        <v>-2.3762</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.7927</v>
+        <v>-2.0251</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6123</v>
+        <v>-0.351</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0406</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0406</v>
+        <v>-2.2893</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0812</v>
+        <v>1.4568</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.0296</v>
+        <v>-0.2655</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2272</v>
+        <v>-0.7458</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8024</v>
+        <v>0.4802</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3975</v>
+        <v>0.7076</v>
       </c>
       <c r="W19" t="n">
-        <v>1.6275</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.23</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="20">
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. HERRERA DOMINGUEZ</t>
+          <t>J. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6499</v>
+        <v>-1.2462</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.207</v>
+        <v>0.4491</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5572</v>
+        <v>-1.6953</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2284</v>
+        <v>1.2398</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1982</v>
+        <v>-1.0535</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0302</v>
+        <v>2.2933</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5792</v>
+        <v>3.0077</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6183999999999999</v>
+        <v>1.2532</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0392</v>
+        <v>1.7545</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6492</v>
+        <v>-1.7679</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5798</v>
+        <v>-2.3067</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0694</v>
+        <v>0.5389</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2081</v>
+        <v>-2.4974</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0406</v>
+        <v>-3.3299</v>
       </c>
       <c r="R21" t="n">
         <v>0.8325</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2133</v>
+        <v>-0.5723</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.3962</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3739</v>
+        <v>-0.1761</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. MARIN ORTEGA</t>
+          <t>A. HERRERA DOMINGUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7986</v>
+        <v>-1.5569</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1276</v>
+        <v>-1.9927</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9262</v>
+        <v>0.4358</v>
       </c>
       <c r="G22" t="n">
-        <v>1.2398</v>
+        <v>-1.2284</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.0535</v>
+        <v>-1.1982</v>
       </c>
       <c r="I22" t="n">
-        <v>2.2933</v>
+        <v>-0.0302</v>
       </c>
       <c r="J22" t="n">
-        <v>3.0077</v>
+        <v>-0.5792</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2532</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>1.7545</v>
+        <v>0.0392</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7679</v>
+        <v>-0.6492</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.3067</v>
+        <v>-0.5798</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5389</v>
+        <v>-0.0694</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.4974</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.3299</v>
+        <v>-1.0406</v>
       </c>
       <c r="R22" t="n">
         <v>0.8325</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1247</v>
+        <v>-0.1204</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7177</v>
+        <v>-0.3729</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4071</v>
+        <v>0.2525</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2578</v>
+        <v>-3.5935</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7899</v>
+        <v>0.5756</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.0477</v>
+        <v>-4.1691</v>
       </c>
       <c r="G23" t="n">
         <v>1.0168</v>
@@ -2248,13 +2248,13 @@
         <v>0.8325</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5787</v>
+        <v>0.243</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3477</v>
+        <v>0.1334</v>
       </c>
       <c r="U23" t="n">
-        <v>0.231</v>
+        <v>0.1096</v>
       </c>
       <c r="V23" t="n">
         <v>-3.3965</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9577</v>
+        <v>-4.1466</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8781</v>
+        <v>-3.0924</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0796</v>
+        <v>-1.0542</v>
       </c>
       <c r="G24" t="n">
         <v>-3.1246</v>
@@ -2326,13 +2326,13 @@
         <v>0.8325</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4156</v>
+        <v>0.2267</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2701</v>
+        <v>0.0557</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1455</v>
+        <v>0.171</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.1338</v>
+        <v>-6.4052</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.6883</v>
+        <v>-6.3669</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4454</v>
+        <v>-0.0383</v>
       </c>
       <c r="G25" t="n">
         <v>-3.1883</v>
@@ -2404,13 +2404,13 @@
         <v>2.0812</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.7374</v>
+        <v>-1.0088</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6929</v>
+        <v>-0.3714</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.0445</v>
+        <v>-0.6374</v>
       </c>
       <c r="V25" t="n">
         <v>-1.1675</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-11.1025</v>
+        <v>-9.6738</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.377699999999999</v>
+        <v>-3.3777</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.7247</v>
+        <v>-6.295999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2649999999999997</v>
+        <v>0.2650000000000006</v>
       </c>
       <c r="H26" t="n">
         <v>-10.2669</v>
@@ -2482,13 +2482,13 @@
         <v>13.5278</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.2029</v>
+        <v>-3.7743</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.7666</v>
+        <v>-2.7667</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.4364</v>
+        <v>-1.0076</v>
       </c>
       <c r="V26" t="n">
         <v>-3.0427</v>
